--- a/outputs/evaluation/architecture/CF_M08_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,57 +481,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Traffic</t>
-        </is>
-      </c>
+          <t>CF_M08_AU24</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Security Service (Traefik)</t>
+          <t>• It communicates with the PostgreSQL database service</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M00_AU02</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>CF_M08_AU04, CF_M08_AU08</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>system service, postgresql</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AU_03</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Traefik</t>
-        </is>
-      </c>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Reverse proxy and load balancer tool.</t>
+          <t>The System Service (Next.js) communicates with the Data Service (PostgreSQL) using Prisma.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.1492</v>
+        <v>0.5987</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
+          <t>CF_M08_AU27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -542,7 +538,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>• It communicates with the PostgreSQL database service</t>
+          <t>• Interacts with various external services for specific functionalities […] Payment processing</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -550,53 +546,49 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU08</t>
+          <t>CF_M08_AU04, CF_M08_AU14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>system service, postgresql</t>
+          <t>system service, payment processing</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Payment Service</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Relational database engine.</t>
+          <t>External service for handling payments and subscriptions.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.4805</v>
+        <v>0.3422</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>React</t>
-        </is>
-      </c>
+          <t>CF_M08_AU28</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>It serves the web application using React</t>
+          <t>• Interacts with various external services for specific functionalities […] Analysis</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -604,34 +596,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M00_AU04</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>CF_M08_AU04, CF_M08_AU16</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>system service, analysis</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Reverse Proxy</t>
-        </is>
-      </c>
+          <t>AU_29</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Traefik acts as an intermediary for client requests, redirecting incoming traffic to the appropriate internal services.</t>
+          <t>The System Service (Next.js) interacts with the Analytics Service (Google Analytics).</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.0467</v>
+        <v>0.2504</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M08_AU25</t>
+          <t>CF_M08_AU29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -642,7 +634,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
+          <t>• Interacts with various external services for specific functionalities [...] Error monitoring</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -650,49 +642,49 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU10</t>
+          <t>CF_M08_AU04, CF_M08_AU18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>system service, authentication</t>
+          <t>system service, error monitoring</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Authentication Service</t>
-        </is>
-      </c>
+          <t>AU_30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>External service for user authentication.</t>
+          <t>The System Service (Next.js) interacts with the Error Tracking Service (Sentry).</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.501</v>
+        <v>0.2517</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M08_AU26</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>CF_M08_AU11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities […] Cloud storage</t>
+          <t>Use Google for user authentication</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -700,49 +692,49 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU12</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>system service, cloud storage</t>
-        </is>
-      </c>
+          <t>CF_M09_AU09</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Storage Service</t>
+          <t>Google Analytics</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>External service for cloud file storage.</t>
+          <t>Analytics tool used for the Analytics Service.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.371</v>
+        <v>0.6296</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M08_AU27</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>CF_M08_AU16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities […] Payment processing</t>
+          <t>Analysis</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -750,49 +742,49 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU14</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>system service, payment processing</t>
-        </is>
-      </c>
+          <t>CF_M08_AD01</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Payment Service</t>
+          <t>Analytics Service</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>External service for handling payments and subscriptions.</t>
+          <t>External service for tracking and analyzing site traffic.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.3477</v>
+        <v>0.2918</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M08_AU28</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>CF_M08_AU18</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Error monitoring</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities […] Analysis</t>
+          <t>Error monitoring</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -800,49 +792,49 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU16</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>system service, analysis</t>
-        </is>
-      </c>
+          <t>CF_M08_AD01</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Analytics Service</t>
+          <t>Error Tracking Service</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>External service for tracking and analyzing site traffic.</t>
+          <t>External service for monitoring and managing application errors.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.1953</v>
+        <v>0.3288</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M08_AU29</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>CF_M08_AU21</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Briefly</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Error monitoring</t>
+          <t>Connects to Brevo to create, send and schedule emails.</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -850,99 +842,95 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU18</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>system service, error monitoring</t>
-        </is>
-      </c>
+          <t>CF_M09_AU19</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Monitoring Service</t>
+          <t>Brevo</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>External service for tracking and managing application errors.</t>
+          <t>Email marketing and communication platform used for the Email Service.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.4194</v>
+        <v>0.0602</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M08_AU30</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>CF_M08_AU23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HTTPS</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Correo electrónico</t>
+          <t>HTTPS, which is the standard for secure communications on the web</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CF_M08_AU04, CF_M08_AU20</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>system service, email</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AU_28</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>System Service to Data Service connection.</t>
+          <t>Individual or entity (donor or company) that interacts with the system.</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.1083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M08_AU16</t>
+          <t>CF_M08_AD02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Analysis</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Analysis</t>
+          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -950,220 +938,74 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M09_AU04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>P_07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Analytics Service</t>
+          <t>ORM (Object-Relational Mapping)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>External service for tracking and analyzing site traffic.</t>
+          <t>Technique used to convert data between the object-oriented programming system and the relational database, implemented via Prisma.</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.2935</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M08_AU21</t>
+          <t>CF_M08_AD06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Briefly</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Connects to Brevo to create, send and schedule emails.</t>
+          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CF_M09_AU19</t>
-        </is>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Brevo</t>
+          <t>Observer Pattern</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Email and marketing communication platform.</t>
+          <t>Establishes a one-to-many relationship where subjects notify observers of state changes, implemented via event listeners in components.</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.0576</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CF_M08_AU23</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>HTTPS</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>HTTPS, which is the standard for secure communications on the web</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>43</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Individual or entity (donor or company) that interacts with the system.</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CF_M08_AD02</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>42</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>CF_M09_AU04</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>AU_25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Prisma ORM</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Object-Relational Mapping tool for database interaction.</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>0.5145999999999999</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CF_M08_AD06</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>78</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Client Component</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Next.js component rendered on the client.</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>0.3476</v>
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,84 +511,80 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>The System Service (Next.js) communicates with the Data Service (PostgreSQL) using Prisma.</t>
+          <t>The System Service communicates with the Data Service (PostgreSQL) using Prisma.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.5987</v>
+        <v>0.6284999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M08_AU27</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>CF_M08_AU23</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HTTPS</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities […] Payment processing</t>
+          <t>HTTPS, which is the standard for secure communications on the web</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CF_M08_AU04, CF_M08_AU14</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>system service, payment processing</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Payment Service</t>
-        </is>
-      </c>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>External service for handling payments and subscriptions.</t>
+          <t>The Security Service (Traefik) routes HTTP/HTTPS traffic to the System Service.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.3422</v>
+        <v>0.3524</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_AU28</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>CF_M08_P02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ORM</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities […] Analysis</t>
+          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,416 +592,74 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU16</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>system service, analysis</t>
-        </is>
-      </c>
+          <t>CF_M09_AU04</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_29</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>P_07</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ORM (Object-Relational Mapping)</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>The System Service (Next.js) interacts with the Analytics Service (Google Analytics).</t>
+          <t>Technique used to convert data between the object-oriented programming system and the relational database, implemented via Prisma.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.2504</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M08_AU29</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>CF_M08_P06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Error monitoring</t>
+          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CF_M08_AU04, CF_M08_AU18</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>system service, error monitoring</t>
-        </is>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_30</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>P_05</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Observer Pattern</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>The System Service (Next.js) interacts with the Error Tracking Service (Sentry).</t>
+          <t>Used to establish a one-to-many relationship where objects (observers) subscribe to a subject to receive notifications of state changes, implemented via event listeners.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.2517</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CF_M08_AU11</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Use Google for user authentication</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>42</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CF_M09_AU09</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Google Analytics</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Analytics tool used for the Analytics Service.</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0.6296</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CF_M08_AU16</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Analysis</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Analysis</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>42</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CF_M08_AD01</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Analytics Service</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>External service for tracking and analyzing site traffic.</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>0.2918</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CF_M08_AU18</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Error monitoring</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Error monitoring</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>42</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CF_M08_AD01</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Error Tracking Service</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>External service for monitoring and managing application errors.</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>0.3288</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CF_M08_AU21</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Briefly</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Connects to Brevo to create, send and schedule emails.</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>42</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CF_M09_AU19</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>AU_20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Brevo</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Email marketing and communication platform used for the Email Service.</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>0.0602</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CF_M08_AU23</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>HTTPS</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>HTTPS, which is the standard for secure communications on the web</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>43</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Individual or entity (donor or company) that interacts with the system.</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M08_AD02</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>42</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CF_M09_AU04</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>P_07</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ORM (Object-Relational Mapping)</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Technique used to convert data between the object-oriented programming system and the relational database, implemented via Prisma.</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0.3491</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CF_M08_AD06</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>78</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Observer Pattern</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Establishes a one-to-many relationship where subjects notify observers of state changes, implemented via event listeners in components.</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>0.24</v>
+        <v>0.2343</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,28 +511,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>The System Service communicates with the Data Service (PostgreSQL) using Prisma.</t>
+          <t>Data Service (PostgreSQL) se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.8529</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M08_AU23</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HTTPS</t>
+          <t>React</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -542,124 +542,82 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HTTPS, which is the standard for secure communications on the web</t>
+          <t>It serves the web application using React</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CF_M08_AU04</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AU_25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>The Security Service (Traefik) routes HTTP/HTTPS traffic to the System Service.</t>
+          <t>Un usuario es todo individuo o entidad que interactúa con el sistema, puede ser tanto un donante como una empresa.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.3524</v>
+        <v>0.6719000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_P02</t>
+          <t>CF_M08_P06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
+          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CF_M09_AU04</t>
-        </is>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>P_07</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ORM (Object-Relational Mapping)</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Technique used to convert data between the object-oriented programming system and the relational database, implemented via Prisma.</t>
+          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.3491</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CF_M08_P06</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>78</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Observer Pattern</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Used to establish a one-to-many relationship where objects (observers) subscribe to a subject to receive notifications of state changes, implemented via event listeners.</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>0.2343</v>
+        <v>0.727</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval_gt_report.xlsx
@@ -481,68 +481,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>CF_M08_AU01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>• It communicates with the PostgreSQL database service</t>
+          <t>These services run on Amazon EC2 instances</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU08</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>system service, postgresql</t>
-        </is>
-      </c>
+          <t>CF_M08_P01</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AU_28</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Data Service (PostgreSQL) se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
+          <t>Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.8529</v>
+        <v>0.7938</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>React</t>
-        </is>
-      </c>
+          <t>CF_M08_AU24</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>It serves the web application using React</t>
+          <t>• It communicates with the PostgreSQL database service</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -550,28 +550,28 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M08_AU04</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>CF_M08_AU04, CF_M08_AU08</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>system service, postgresql</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
+          <t>AU_27</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Un usuario es todo individuo o entidad que interactúa con el sistema, puede ser tanto un donante como una empresa.</t>
+          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.8608</v>
       </c>
     </row>
     <row r="4">
@@ -603,21 +603,17 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+          <t>AU_30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
+          <t>Al interactuar con un componente de cliente, este puede acceder al servidor mediante el uso de las server actions.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.727</v>
+        <v>0.8107</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,7 +521,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -567,53 +567,149 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
+          <t>Data Service (PostgreSQL) [...] Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.8608</v>
+        <v>0.8547</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_P06</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
+          <t>CF_M08_AU25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
+          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>78</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CF_M08_AU04, CF_M08_AU10, CF_M08_AU12, CF_M08_AU14, CF_M08_AU16, CF_M08_AU18, CF_M08_AU20</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>system service, authentication, cloud storage, payment processing, analytics, error monitoring, email</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Authentication Service</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Al interactuar con un componente de cliente, este puede acceder al servidor mediante el uso de las server actions.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.8107</v>
+        <v>0.8391</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CF_M08_AU23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HTTPS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HTTPS, which is the standard for secure communications on the web</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>43</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Security Service (Traefik) [...] Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7383</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CF_M08_P06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>78</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Un usuario es todo individuo o entidad que interactúa con el sistema, puede ser tanto un donante como una empresa.</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.714</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
+          <t>Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -567,43 +567,39 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Data Service (PostgreSQL) [...] Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
+          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.8547</v>
+        <v>0.8608</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_AU25</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>CF_M08_P06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
+          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CF_M08_AU04, CF_M08_AU10, CF_M08_AU12, CF_M08_AU14, CF_M08_AU16, CF_M08_AU18, CF_M08_AU20</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>system service, authentication, cloud storage, payment processing, analytics, error monitoring, email</t>
-        </is>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
@@ -612,104 +608,16 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Authentication Service</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios.</t>
+          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.8391</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CF_M08_AU23</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>HTTPS</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HTTPS, which is the standard for secure communications on the web</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>43</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Security Service (Traefik) [...] Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>0.7383</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CF_M08_P06</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>78</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Un usuario es todo individuo o entidad que interactúa con el sistema, puede ser tanto un donante como una empresa.</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0.714</v>
+        <v>0.727</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -561,62 +561,108 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
+          <t>Data Service (PostgreSQL) se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.8608</v>
+        <v>0.8529</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_P06</t>
+          <t>CF_M08_P02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
+          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>78</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CF_M08_AU04</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+          <t>AU_27</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>System Service (Next.js) se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.673</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CF_M08_P06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>78</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>HTTP</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Traefik abre el puerto 80 para manejar tráfico HTTP no seguro.</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
         <v>0.727</v>
       </c>
     </row>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval_gt_report.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>GT_fixes</t>
+          <t>GT_fixedType</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -511,7 +511,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -561,38 +561,38 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AU_29</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>AU_07</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PostgreSQL</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Data Service (PostgreSQL) se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
+          <t>Proporciona la base de datos relacional para almacenar los datos de la aplicación.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.8529</v>
+        <v>0.8507</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_P02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
+          <t>CF_M08_AU25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
+          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -600,24 +600,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M08_AU04</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>CF_M08_AU04, CF_M08_AU10, CF_M08_AU12, CF_M08_AU14, CF_M08_AU16, CF_M08_AU18, CF_M08_AU20</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>system service, authentication, cloud storage, payment processing, analytics, error monitoring, email</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Authentication Service</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>System Service (Next.js) se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.673</v>
+        <v>0.8391</v>
       </c>
     </row>
     <row r="5">
@@ -649,7 +657,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -659,7 +667,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Traefik abre el puerto 80 para manejar tráfico HTTP no seguro.</t>
+          <t>Traefik abre el puerto 80 para manejar tráfico HTTP.</t>
         </is>
       </c>
       <c r="L5" t="n">
